--- a/backtest_runs/20260410_193731/by_symbol/SAZEW/SAZEW.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SAZEW/SAZEW.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-1332.650000000001</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>104532</v>
@@ -679,7 +679,7 @@
         <v>-11727.1</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>92804.90000000001</v>
@@ -771,7 +771,7 @@
         <v>-1256.750000000008</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>93908.75</v>
@@ -817,7 +817,7 @@
         <v>-3737.800000000002</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>90170.95</v>
@@ -863,7 +863,7 @@
         <v>-1569.149999999998</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>88601.8</v>
@@ -909,7 +909,7 @@
         <v>-2934.249999999995</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>85667.55</v>
@@ -1047,7 +1047,7 @@
         <v>-2445.300000000002</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>86918.8</v>
@@ -1093,7 +1093,7 @@
         <v>-3036.550000000002</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>83882.25</v>
@@ -1185,7 +1185,7 @@
         <v>-3614.050000000002</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>80355.64999999999</v>
@@ -1231,7 +1231,7 @@
         <v>-2256.649999999999</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>78099</v>
@@ -1277,7 +1277,7 @@
         <v>-5422.449999999995</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>72676.55</v>
@@ -1415,7 +1415,7 @@
         <v>-1975.599999999991</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>78034.65000000001</v>
@@ -1461,7 +1461,7 @@
         <v>-2467.850000000007</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>75566.8</v>
@@ -1553,7 +1553,7 @@
         <v>-215.0500000000045</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>76834</v>
